--- a/wwwroot/template/TemplateApprover.xlsx
+++ b/wwwroot/template/TemplateApprover.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khanhmf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB223D9-5180-494C-83D5-A223C6792A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA2F018-0942-4F56-B83B-4A37C7DB15AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B626CB9-29FE-4B5C-9389-803B2A743CD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B626CB9-29FE-4B5C-9389-803B2A743CD7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>No</t>
   </si>
@@ -186,6 +186,16 @@
   <si>
     <t>Mã đơn yêu cầu
 Request Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID request
+</t>
+  </si>
+  <si>
+    <t>Step quotion request</t>
+  </si>
+  <si>
+    <t>Status quotion request</t>
   </si>
 </sst>
 </file>
@@ -281,15 +291,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -298,15 +315,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -642,75 +658,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6533764C-5086-42D3-9113-666D7A7B28C0}">
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="35" width="9.140625" style="7"/>
-    <col min="36" max="36" width="13.42578125" style="7" customWidth="1"/>
+    <col min="1" max="30" width="9.140625" style="3"/>
+    <col min="31" max="31" width="18.42578125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="17.85546875" style="3" customWidth="1"/>
+    <col min="33" max="35" width="9.140625" style="3"/>
+    <col min="36" max="37" width="9.140625" style="3" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="9.140625" style="3"/>
+    <col min="39" max="39" width="13.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="4">
         <v>2</v>
       </c>
       <c r="C1" s="1">
         <v>3</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D1" s="4">
         <v>4</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E1" s="4">
         <v>5</v>
       </c>
-      <c r="F1" s="1">
+      <c r="F1" s="4">
         <v>6</v>
       </c>
-      <c r="G1" s="1">
+      <c r="G1" s="4">
         <v>7</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H1" s="4">
         <v>8</v>
       </c>
-      <c r="I1" s="1">
+      <c r="I1" s="4">
         <v>9</v>
       </c>
-      <c r="J1" s="1">
+      <c r="J1" s="4">
         <v>10</v>
       </c>
-      <c r="K1" s="1">
+      <c r="K1" s="4">
         <v>11</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L1" s="4">
         <v>12</v>
       </c>
-      <c r="M1" s="1">
+      <c r="M1" s="4">
         <v>13</v>
       </c>
-      <c r="N1" s="6">
-        <f>M1+1</f>
+      <c r="N1" s="4">
         <v>14</v>
       </c>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="1">
+      <c r="O1" s="10">
+        <f>N1+1</f>
         <v>15</v>
       </c>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
       <c r="U1" s="1">
-        <f>T1+1</f>
         <v>16</v>
       </c>
       <c r="V1" s="1">
-        <f t="shared" ref="U1:AJ1" si="0">U1+1</f>
+        <f>U1+1</f>
         <v>17</v>
       </c>
       <c r="W1" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="W1:AM1" si="0">V1+1</f>
         <v>18</v>
       </c>
       <c r="X1" s="1">
@@ -757,192 +777,198 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="AI1" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AJ1" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
+      <c r="AK1" s="5">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="AL1" s="1">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="AM1" s="1">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3" t="s">
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="Y2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Z2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="AA2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AB2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AC2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AD2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AE2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AF2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AG2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AG2" s="3" t="s">
+      <c r="AH2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AI2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AI2" s="9" t="s">
+      <c r="AJ2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AJ2" s="9" t="s">
+      <c r="AM2" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="5" t="s">
+    <row r="3" spans="1:39" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="T3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="9"/>
-      <c r="AJ3" s="9"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="8"/>
+      <c r="AE3" s="8"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
+      <c r="AI3" s="8"/>
+      <c r="AJ3" s="8"/>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
+  <mergeCells count="35">
+    <mergeCell ref="U2:U3"/>
     <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="AK2:AK3"/>
     <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
     <mergeCell ref="V2:V3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:S2"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="O1:T1"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
@@ -950,9 +976,30 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:T2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI4:AI572" xr:uid="{14644A99-9082-4B01-8C22-E7F4A3B3E531}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL4:AL572" xr:uid="{14644A99-9082-4B01-8C22-E7F4A3B3E531}">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/wwwroot/template/TemplateApprover.xlsx
+++ b/wwwroot/template/TemplateApprover.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA2F018-0942-4F56-B83B-4A37C7DB15AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456A7689-B1D9-4FE0-B3F6-36C5796937F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B626CB9-29FE-4B5C-9389-803B2A743CD7}"/>
+    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{8B626CB9-29FE-4B5C-9389-803B2A743CD7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -291,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -300,10 +300,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -312,17 +315,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -674,54 +668,54 @@
       <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="4">
+      <c r="B1" s="1">
         <v>2</v>
       </c>
       <c r="C1" s="1">
         <v>3</v>
       </c>
-      <c r="D1" s="4">
+      <c r="D1" s="1">
         <v>4</v>
       </c>
-      <c r="E1" s="4">
+      <c r="E1" s="1">
         <v>5</v>
       </c>
-      <c r="F1" s="4">
+      <c r="F1" s="1">
         <v>6</v>
       </c>
-      <c r="G1" s="4">
+      <c r="G1" s="1">
         <v>7</v>
       </c>
-      <c r="H1" s="4">
+      <c r="H1" s="1">
         <v>8</v>
       </c>
-      <c r="I1" s="4">
+      <c r="I1" s="1">
         <v>9</v>
       </c>
-      <c r="J1" s="4">
+      <c r="J1" s="1">
         <v>10</v>
       </c>
-      <c r="K1" s="4">
+      <c r="K1" s="1">
         <v>11</v>
       </c>
-      <c r="L1" s="4">
+      <c r="L1" s="1">
         <v>12</v>
       </c>
-      <c r="M1" s="4">
+      <c r="M1" s="1">
         <v>13</v>
       </c>
-      <c r="N1" s="4">
+      <c r="N1" s="1">
         <v>14</v>
       </c>
-      <c r="O1" s="10">
+      <c r="O1" s="5">
         <f>N1+1</f>
         <v>15</v>
       </c>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
       <c r="U1" s="1">
         <v>16</v>
       </c>
@@ -777,15 +771,15 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AI1" s="5">
+      <c r="AI1" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="AJ1" s="5">
+      <c r="AJ1" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="AK1" s="5">
+      <c r="AK1" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -799,105 +793,105 @@
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8" t="s">
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="V2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="X2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" s="8" t="s">
+      <c r="Y2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Z2" s="8" t="s">
+      <c r="Z2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AA2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AB2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AC2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AD2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AE2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AF2" s="8" t="s">
+      <c r="AF2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AG2" s="8" t="s">
+      <c r="AG2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AH2" s="8" t="s">
+      <c r="AH2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AI2" s="8" t="s">
+      <c r="AI2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AJ2" s="8" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AK2" s="8" t="s">
+      <c r="AK2" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AL2" s="9" t="s">
@@ -908,20 +902,20 @@
       </c>
     </row>
     <row r="3" spans="1:39" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
       <c r="O3" s="2" t="s">
         <v>28</v>
       </c>
@@ -940,33 +934,42 @@
       <c r="T3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8"/>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
-      <c r="AI3" s="8"/>
-      <c r="AJ3" s="8"/>
-      <c r="AK3" s="8"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
       <c r="AL3" s="9"/>
       <c r="AM3" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
     <mergeCell ref="O1:T1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="D2:D3"/>
@@ -982,21 +985,12 @@
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:T2"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="V2:V3"/>
     <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL4:AL572" xr:uid="{14644A99-9082-4B01-8C22-E7F4A3B3E531}">
